--- a/data_pengguna.xlsx
+++ b/data_pengguna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F971EC7-3661-40A6-90C0-D14C6E7DC653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2A7D3E-F7E6-4FE1-9A3D-2D0FD325FC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FBB3284E-7124-44F4-ACFD-447A6886AA12}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="105">
   <si>
     <t>NO REGISTRASI</t>
   </si>
@@ -298,6 +298,48 @@
   </si>
   <si>
     <t>GO Kemakmuran</t>
+  </si>
+  <si>
+    <t>PU 1</t>
+  </si>
+  <si>
+    <t>PK 1</t>
+  </si>
+  <si>
+    <t>PPU 1</t>
+  </si>
+  <si>
+    <t>PBM 1</t>
+  </si>
+  <si>
+    <t>Lit Bhs Indo 1</t>
+  </si>
+  <si>
+    <t>Lit Bhs Ing 1</t>
+  </si>
+  <si>
+    <t>PU 2</t>
+  </si>
+  <si>
+    <t>PK 2</t>
+  </si>
+  <si>
+    <t>PPU 2</t>
+  </si>
+  <si>
+    <t>PBM 2</t>
+  </si>
+  <si>
+    <t>Lit Bhs Indo 2</t>
+  </si>
+  <si>
+    <t>Lit Bhs Ing 2</t>
+  </si>
+  <si>
+    <t>PM 2</t>
+  </si>
+  <si>
+    <t>PM 1</t>
   </si>
 </sst>
 </file>
@@ -1829,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E436D765-1505-4BA4-BDA9-9A238174077E}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="8" bestFit="1" customWidth="1"/>
@@ -1843,7 +1885,7 @@
     <col min="10" max="10" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>85</v>
       </c>
@@ -1880,8 +1922,50 @@
       <c r="L1" s="5" t="s">
         <v>89</v>
       </c>
+      <c r="M1" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>103</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>8121012331</v>
       </c>
@@ -1916,8 +2000,57 @@
       <c r="L2" t="s">
         <v>90</v>
       </c>
+      <c r="M2">
+        <v>654</v>
+      </c>
+      <c r="N2">
+        <v>653</v>
+      </c>
+      <c r="O2">
+        <v>650</v>
+      </c>
+      <c r="P2">
+        <v>664</v>
+      </c>
+      <c r="Q2">
+        <v>663</v>
+      </c>
+      <c r="R2">
+        <v>661</v>
+      </c>
+      <c r="S2">
+        <v>633</v>
+      </c>
+      <c r="T2">
+        <f>M2+5</f>
+        <v>659</v>
+      </c>
+      <c r="U2">
+        <f>N2+6</f>
+        <v>659</v>
+      </c>
+      <c r="V2">
+        <f>O2+7</f>
+        <v>657</v>
+      </c>
+      <c r="W2">
+        <f>P2+9</f>
+        <v>673</v>
+      </c>
+      <c r="X2">
+        <f>Q2-4</f>
+        <v>659</v>
+      </c>
+      <c r="Y2">
+        <f>R2+7</f>
+        <v>668</v>
+      </c>
+      <c r="Z2">
+        <f>S2-4</f>
+        <v>629</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>89646647103</v>
       </c>
@@ -1954,8 +2087,57 @@
       <c r="L3" t="s">
         <v>90</v>
       </c>
+      <c r="M3">
+        <v>654</v>
+      </c>
+      <c r="N3">
+        <v>645</v>
+      </c>
+      <c r="O3">
+        <v>651</v>
+      </c>
+      <c r="P3">
+        <v>664</v>
+      </c>
+      <c r="Q3">
+        <v>663</v>
+      </c>
+      <c r="R3">
+        <v>661</v>
+      </c>
+      <c r="S3">
+        <v>633</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T30" si="0">M3+5</f>
+        <v>659</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U30" si="1">N3+6</f>
+        <v>651</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V30" si="2">O3+7</f>
+        <v>658</v>
+      </c>
+      <c r="W3">
+        <f t="shared" ref="W3:W30" si="3">P3+9</f>
+        <v>673</v>
+      </c>
+      <c r="X3">
+        <f t="shared" ref="X3:X30" si="4">Q3-4</f>
+        <v>659</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" ref="Y3:Y30" si="5">R3+7</f>
+        <v>668</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" ref="Z3:Z30" si="6">S3-4</f>
+        <v>629</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>89676992669</v>
       </c>
@@ -1992,8 +2174,57 @@
       <c r="L4" t="s">
         <v>90</v>
       </c>
+      <c r="M4">
+        <v>654</v>
+      </c>
+      <c r="N4">
+        <v>637</v>
+      </c>
+      <c r="O4">
+        <v>652</v>
+      </c>
+      <c r="P4">
+        <v>664</v>
+      </c>
+      <c r="Q4">
+        <v>663</v>
+      </c>
+      <c r="R4">
+        <v>661</v>
+      </c>
+      <c r="S4">
+        <v>633</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="1"/>
+        <v>643</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="2"/>
+        <v>659</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>81362323239</v>
       </c>
@@ -2030,8 +2261,57 @@
       <c r="L5" t="s">
         <v>90</v>
       </c>
+      <c r="M5">
+        <v>654</v>
+      </c>
+      <c r="N5">
+        <v>629</v>
+      </c>
+      <c r="O5">
+        <v>653</v>
+      </c>
+      <c r="P5">
+        <v>664</v>
+      </c>
+      <c r="Q5">
+        <v>663</v>
+      </c>
+      <c r="R5">
+        <v>661</v>
+      </c>
+      <c r="S5">
+        <v>633</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="1"/>
+        <v>635</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>8561716571</v>
       </c>
@@ -2068,8 +2348,57 @@
       <c r="L6" t="s">
         <v>90</v>
       </c>
+      <c r="M6">
+        <v>654</v>
+      </c>
+      <c r="N6">
+        <v>621</v>
+      </c>
+      <c r="O6">
+        <v>654</v>
+      </c>
+      <c r="P6">
+        <v>664</v>
+      </c>
+      <c r="Q6">
+        <v>663</v>
+      </c>
+      <c r="R6">
+        <v>661</v>
+      </c>
+      <c r="S6">
+        <v>633</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="1"/>
+        <v>627</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="2"/>
+        <v>661</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>8121068945</v>
       </c>
@@ -2106,8 +2435,57 @@
       <c r="L7" t="s">
         <v>90</v>
       </c>
+      <c r="M7">
+        <v>654</v>
+      </c>
+      <c r="N7">
+        <v>613</v>
+      </c>
+      <c r="O7">
+        <v>655</v>
+      </c>
+      <c r="P7">
+        <v>664</v>
+      </c>
+      <c r="Q7">
+        <v>663</v>
+      </c>
+      <c r="R7">
+        <v>661</v>
+      </c>
+      <c r="S7">
+        <v>633</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="1"/>
+        <v>619</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="2"/>
+        <v>662</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>8111105900</v>
       </c>
@@ -2144,8 +2522,57 @@
       <c r="L8" t="s">
         <v>90</v>
       </c>
+      <c r="M8">
+        <v>654</v>
+      </c>
+      <c r="N8">
+        <v>605</v>
+      </c>
+      <c r="O8">
+        <v>656</v>
+      </c>
+      <c r="P8">
+        <v>664</v>
+      </c>
+      <c r="Q8">
+        <v>663</v>
+      </c>
+      <c r="R8">
+        <v>661</v>
+      </c>
+      <c r="S8">
+        <v>633</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="1"/>
+        <v>611</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="2"/>
+        <v>663</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>81380317979</v>
       </c>
@@ -2182,8 +2609,57 @@
       <c r="L9" t="s">
         <v>90</v>
       </c>
+      <c r="M9">
+        <v>654</v>
+      </c>
+      <c r="N9">
+        <v>597</v>
+      </c>
+      <c r="O9">
+        <v>657</v>
+      </c>
+      <c r="P9">
+        <v>664</v>
+      </c>
+      <c r="Q9">
+        <v>663</v>
+      </c>
+      <c r="R9">
+        <v>661</v>
+      </c>
+      <c r="S9">
+        <v>633</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="1"/>
+        <v>603</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="2"/>
+        <v>664</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>8111093977</v>
       </c>
@@ -2218,8 +2694,57 @@
       <c r="L10" t="s">
         <v>90</v>
       </c>
+      <c r="M10">
+        <v>654</v>
+      </c>
+      <c r="N10">
+        <v>589</v>
+      </c>
+      <c r="O10">
+        <v>658</v>
+      </c>
+      <c r="P10">
+        <v>664</v>
+      </c>
+      <c r="Q10">
+        <v>663</v>
+      </c>
+      <c r="R10">
+        <v>661</v>
+      </c>
+      <c r="S10">
+        <v>633</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="1"/>
+        <v>595</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="2"/>
+        <v>665</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>81937815758</v>
       </c>
@@ -2256,8 +2781,57 @@
       <c r="L11" t="s">
         <v>90</v>
       </c>
+      <c r="M11">
+        <v>654</v>
+      </c>
+      <c r="N11">
+        <v>581</v>
+      </c>
+      <c r="O11">
+        <v>659</v>
+      </c>
+      <c r="P11">
+        <v>664</v>
+      </c>
+      <c r="Q11">
+        <v>663</v>
+      </c>
+      <c r="R11">
+        <v>661</v>
+      </c>
+      <c r="S11">
+        <v>633</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="1"/>
+        <v>587</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="2"/>
+        <v>666</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>85319838851</v>
       </c>
@@ -2294,8 +2868,57 @@
       <c r="L12" t="s">
         <v>90</v>
       </c>
+      <c r="M12">
+        <v>654</v>
+      </c>
+      <c r="N12">
+        <v>573</v>
+      </c>
+      <c r="O12">
+        <v>660</v>
+      </c>
+      <c r="P12">
+        <v>664</v>
+      </c>
+      <c r="Q12">
+        <v>663</v>
+      </c>
+      <c r="R12">
+        <v>661</v>
+      </c>
+      <c r="S12">
+        <v>633</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="1"/>
+        <v>579</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="2"/>
+        <v>667</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>82299482917</v>
       </c>
@@ -2332,8 +2955,57 @@
       <c r="L13" t="s">
         <v>90</v>
       </c>
+      <c r="M13">
+        <v>654</v>
+      </c>
+      <c r="N13">
+        <v>565</v>
+      </c>
+      <c r="O13">
+        <v>661</v>
+      </c>
+      <c r="P13">
+        <v>664</v>
+      </c>
+      <c r="Q13">
+        <v>663</v>
+      </c>
+      <c r="R13">
+        <v>661</v>
+      </c>
+      <c r="S13">
+        <v>633</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="1"/>
+        <v>571</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="2"/>
+        <v>668</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>8121080579</v>
       </c>
@@ -2368,8 +3040,57 @@
       <c r="L14" t="s">
         <v>90</v>
       </c>
+      <c r="M14">
+        <v>654</v>
+      </c>
+      <c r="N14">
+        <v>557</v>
+      </c>
+      <c r="O14">
+        <v>662</v>
+      </c>
+      <c r="P14">
+        <v>664</v>
+      </c>
+      <c r="Q14">
+        <v>663</v>
+      </c>
+      <c r="R14">
+        <v>661</v>
+      </c>
+      <c r="S14">
+        <v>633</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="1"/>
+        <v>563</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="2"/>
+        <v>669</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>81808655655</v>
       </c>
@@ -2406,8 +3127,57 @@
       <c r="L15" t="s">
         <v>90</v>
       </c>
+      <c r="M15">
+        <v>654</v>
+      </c>
+      <c r="N15">
+        <v>549</v>
+      </c>
+      <c r="O15">
+        <v>663</v>
+      </c>
+      <c r="P15">
+        <v>664</v>
+      </c>
+      <c r="Q15">
+        <v>663</v>
+      </c>
+      <c r="R15">
+        <v>661</v>
+      </c>
+      <c r="S15">
+        <v>633</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="1"/>
+        <v>555</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="2"/>
+        <v>670</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>8567430855</v>
       </c>
@@ -2442,8 +3212,57 @@
       <c r="L16" t="s">
         <v>90</v>
       </c>
+      <c r="M16">
+        <v>654</v>
+      </c>
+      <c r="N16">
+        <v>541</v>
+      </c>
+      <c r="O16">
+        <v>664</v>
+      </c>
+      <c r="P16">
+        <v>664</v>
+      </c>
+      <c r="Q16">
+        <v>663</v>
+      </c>
+      <c r="R16">
+        <v>661</v>
+      </c>
+      <c r="S16">
+        <v>633</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="1"/>
+        <v>547</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="2"/>
+        <v>671</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>81932254383</v>
       </c>
@@ -2478,8 +3297,57 @@
       <c r="L17" t="s">
         <v>90</v>
       </c>
+      <c r="M17">
+        <v>654</v>
+      </c>
+      <c r="N17">
+        <v>533</v>
+      </c>
+      <c r="O17">
+        <v>665</v>
+      </c>
+      <c r="P17">
+        <v>664</v>
+      </c>
+      <c r="Q17">
+        <v>663</v>
+      </c>
+      <c r="R17">
+        <v>661</v>
+      </c>
+      <c r="S17">
+        <v>633</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="1"/>
+        <v>539</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="2"/>
+        <v>672</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X17">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>137711099</v>
       </c>
@@ -2516,8 +3384,57 @@
       <c r="L18" t="s">
         <v>90</v>
       </c>
+      <c r="M18">
+        <v>654</v>
+      </c>
+      <c r="N18">
+        <v>525</v>
+      </c>
+      <c r="O18">
+        <v>666</v>
+      </c>
+      <c r="P18">
+        <v>664</v>
+      </c>
+      <c r="Q18">
+        <v>663</v>
+      </c>
+      <c r="R18">
+        <v>661</v>
+      </c>
+      <c r="S18">
+        <v>633</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="1"/>
+        <v>531</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="2"/>
+        <v>673</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X18">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z18">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>8128151949</v>
       </c>
@@ -2554,8 +3471,57 @@
       <c r="L19" t="s">
         <v>90</v>
       </c>
+      <c r="M19">
+        <v>654</v>
+      </c>
+      <c r="N19">
+        <v>517</v>
+      </c>
+      <c r="O19">
+        <v>667</v>
+      </c>
+      <c r="P19">
+        <v>664</v>
+      </c>
+      <c r="Q19">
+        <v>663</v>
+      </c>
+      <c r="R19">
+        <v>661</v>
+      </c>
+      <c r="S19">
+        <v>633</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="1"/>
+        <v>523</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="2"/>
+        <v>674</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>82118004385</v>
       </c>
@@ -2592,8 +3558,57 @@
       <c r="L20" t="s">
         <v>90</v>
       </c>
+      <c r="M20">
+        <v>654</v>
+      </c>
+      <c r="N20">
+        <v>509</v>
+      </c>
+      <c r="O20">
+        <v>668</v>
+      </c>
+      <c r="P20">
+        <v>664</v>
+      </c>
+      <c r="Q20">
+        <v>663</v>
+      </c>
+      <c r="R20">
+        <v>661</v>
+      </c>
+      <c r="S20">
+        <v>633</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="1"/>
+        <v>515</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="2"/>
+        <v>675</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>85881971197</v>
       </c>
@@ -2630,8 +3645,57 @@
       <c r="L21" t="s">
         <v>90</v>
       </c>
+      <c r="M21">
+        <v>654</v>
+      </c>
+      <c r="N21">
+        <v>501</v>
+      </c>
+      <c r="O21">
+        <v>669</v>
+      </c>
+      <c r="P21">
+        <v>664</v>
+      </c>
+      <c r="Q21">
+        <v>663</v>
+      </c>
+      <c r="R21">
+        <v>661</v>
+      </c>
+      <c r="S21">
+        <v>633</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="1"/>
+        <v>507</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="2"/>
+        <v>676</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X21">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z21">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>81280734514</v>
       </c>
@@ -2668,8 +3732,57 @@
       <c r="L22" t="s">
         <v>90</v>
       </c>
+      <c r="M22">
+        <v>654</v>
+      </c>
+      <c r="N22">
+        <v>493</v>
+      </c>
+      <c r="O22">
+        <v>670</v>
+      </c>
+      <c r="P22">
+        <v>664</v>
+      </c>
+      <c r="Q22">
+        <v>663</v>
+      </c>
+      <c r="R22">
+        <v>661</v>
+      </c>
+      <c r="S22">
+        <v>633</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="1"/>
+        <v>499</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="2"/>
+        <v>677</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X22">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z22">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>81320533210</v>
       </c>
@@ -2706,8 +3819,57 @@
       <c r="L23" t="s">
         <v>90</v>
       </c>
+      <c r="M23">
+        <v>654</v>
+      </c>
+      <c r="N23">
+        <v>485</v>
+      </c>
+      <c r="O23">
+        <v>671</v>
+      </c>
+      <c r="P23">
+        <v>664</v>
+      </c>
+      <c r="Q23">
+        <v>663</v>
+      </c>
+      <c r="R23">
+        <v>661</v>
+      </c>
+      <c r="S23">
+        <v>633</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="1"/>
+        <v>491</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="2"/>
+        <v>678</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X23">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z23">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>8151616679</v>
       </c>
@@ -2742,8 +3904,57 @@
       <c r="L24" t="s">
         <v>90</v>
       </c>
+      <c r="M24">
+        <v>654</v>
+      </c>
+      <c r="N24">
+        <v>477</v>
+      </c>
+      <c r="O24">
+        <v>672</v>
+      </c>
+      <c r="P24">
+        <v>664</v>
+      </c>
+      <c r="Q24">
+        <v>663</v>
+      </c>
+      <c r="R24">
+        <v>661</v>
+      </c>
+      <c r="S24">
+        <v>633</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="1"/>
+        <v>483</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="2"/>
+        <v>679</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X24">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z24">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>8561108006</v>
       </c>
@@ -2780,8 +3991,57 @@
       <c r="L25" t="s">
         <v>90</v>
       </c>
+      <c r="M25">
+        <v>654</v>
+      </c>
+      <c r="N25">
+        <v>469</v>
+      </c>
+      <c r="O25">
+        <v>673</v>
+      </c>
+      <c r="P25">
+        <v>664</v>
+      </c>
+      <c r="Q25">
+        <v>663</v>
+      </c>
+      <c r="R25">
+        <v>661</v>
+      </c>
+      <c r="S25">
+        <v>633</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="1"/>
+        <v>475</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="2"/>
+        <v>680</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z25">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>8119698384</v>
       </c>
@@ -2818,8 +4078,57 @@
       <c r="L26" t="s">
         <v>90</v>
       </c>
+      <c r="M26">
+        <v>654</v>
+      </c>
+      <c r="N26">
+        <v>461</v>
+      </c>
+      <c r="O26">
+        <v>674</v>
+      </c>
+      <c r="P26">
+        <v>664</v>
+      </c>
+      <c r="Q26">
+        <v>663</v>
+      </c>
+      <c r="R26">
+        <v>661</v>
+      </c>
+      <c r="S26">
+        <v>633</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="1"/>
+        <v>467</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="2"/>
+        <v>681</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>81219661720</v>
       </c>
@@ -2856,8 +4165,57 @@
       <c r="L27" t="s">
         <v>90</v>
       </c>
+      <c r="M27">
+        <v>654</v>
+      </c>
+      <c r="N27">
+        <v>453</v>
+      </c>
+      <c r="O27">
+        <v>675</v>
+      </c>
+      <c r="P27">
+        <v>664</v>
+      </c>
+      <c r="Q27">
+        <v>663</v>
+      </c>
+      <c r="R27">
+        <v>661</v>
+      </c>
+      <c r="S27">
+        <v>633</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U27">
+        <f t="shared" si="1"/>
+        <v>459</v>
+      </c>
+      <c r="V27">
+        <f t="shared" si="2"/>
+        <v>682</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X27">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y27">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z27">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>81389744244</v>
       </c>
@@ -2894,8 +4252,57 @@
       <c r="L28" t="s">
         <v>90</v>
       </c>
+      <c r="M28">
+        <v>654</v>
+      </c>
+      <c r="N28">
+        <v>445</v>
+      </c>
+      <c r="O28">
+        <v>676</v>
+      </c>
+      <c r="P28">
+        <v>664</v>
+      </c>
+      <c r="Q28">
+        <v>663</v>
+      </c>
+      <c r="R28">
+        <v>661</v>
+      </c>
+      <c r="S28">
+        <v>633</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U28">
+        <f t="shared" si="1"/>
+        <v>451</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="2"/>
+        <v>683</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X28">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>85210398995</v>
       </c>
@@ -2932,8 +4339,57 @@
       <c r="L29" t="s">
         <v>90</v>
       </c>
+      <c r="M29">
+        <v>654</v>
+      </c>
+      <c r="N29">
+        <v>437</v>
+      </c>
+      <c r="O29">
+        <v>677</v>
+      </c>
+      <c r="P29">
+        <v>664</v>
+      </c>
+      <c r="Q29">
+        <v>663</v>
+      </c>
+      <c r="R29">
+        <v>661</v>
+      </c>
+      <c r="S29">
+        <v>633</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U29">
+        <f t="shared" si="1"/>
+        <v>443</v>
+      </c>
+      <c r="V29">
+        <f t="shared" si="2"/>
+        <v>684</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X29">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z29">
+        <f t="shared" si="6"/>
+        <v>629</v>
+      </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>88212209977</v>
       </c>
@@ -2969,6 +4425,55 @@
       </c>
       <c r="L30" t="s">
         <v>90</v>
+      </c>
+      <c r="M30">
+        <v>654</v>
+      </c>
+      <c r="N30">
+        <v>429</v>
+      </c>
+      <c r="O30">
+        <v>678</v>
+      </c>
+      <c r="P30">
+        <v>664</v>
+      </c>
+      <c r="Q30">
+        <v>663</v>
+      </c>
+      <c r="R30">
+        <v>661</v>
+      </c>
+      <c r="S30">
+        <v>633</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="U30">
+        <f t="shared" si="1"/>
+        <v>435</v>
+      </c>
+      <c r="V30">
+        <f t="shared" si="2"/>
+        <v>685</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="3"/>
+        <v>673</v>
+      </c>
+      <c r="X30">
+        <f t="shared" si="4"/>
+        <v>659</v>
+      </c>
+      <c r="Y30">
+        <f t="shared" si="5"/>
+        <v>668</v>
+      </c>
+      <c r="Z30">
+        <f t="shared" si="6"/>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -2982,7 +4487,7 @@
     <cfRule type="duplicateValues" dxfId="104" priority="7"/>
     <cfRule type="duplicateValues" dxfId="103" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:L1">
+  <conditionalFormatting sqref="A1:Z1">
     <cfRule type="duplicateValues" dxfId="102" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
@@ -3096,7 +4601,7 @@
     <cfRule type="duplicateValues" dxfId="4" priority="18"/>
     <cfRule type="duplicateValues" dxfId="3" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1 I1:L1">
+  <conditionalFormatting sqref="G1 I1:Z1">
     <cfRule type="duplicateValues" dxfId="2" priority="11"/>
     <cfRule type="duplicateValues" dxfId="1" priority="10"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>

--- a/data_pengguna.xlsx
+++ b/data_pengguna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1205BCB8-6867-4DCB-9FCB-0DC7C53B5C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F5C94D-3273-469B-B870-11A5D610E3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FBB3284E-7124-44F4-ACFD-447A6886AA12}"/>
   </bookViews>
@@ -2076,25 +2076,25 @@
     <cfRule type="duplicateValues" dxfId="102" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="101" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="80"/>
     <cfRule type="duplicateValues" dxfId="92" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="76"/>
     <cfRule type="duplicateValues" dxfId="82" priority="89"/>
     <cfRule type="duplicateValues" dxfId="81" priority="90"/>
     <cfRule type="duplicateValues" dxfId="80" priority="91"/>
@@ -2104,92 +2104,90 @@
     <cfRule type="duplicateValues" dxfId="76" priority="95"/>
     <cfRule type="duplicateValues" dxfId="75" priority="96"/>
     <cfRule type="duplicateValues" dxfId="74" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="88"/>
     <cfRule type="duplicateValues" dxfId="72" priority="99"/>
     <cfRule type="duplicateValues" dxfId="71" priority="100"/>
     <cfRule type="duplicateValues" dxfId="70" priority="101"/>
     <cfRule type="duplicateValues" dxfId="69" priority="102"/>
     <cfRule type="duplicateValues" dxfId="68" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="aboveAverage" dxfId="60" priority="34" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="51"/>
-    <cfRule type="aboveAverage" dxfId="42" priority="52" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="68"/>
-    <cfRule type="aboveAverage" dxfId="25" priority="69" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="62"/>
+    <cfRule type="aboveAverage" dxfId="55" priority="34" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="68"/>
+    <cfRule type="aboveAverage" dxfId="49" priority="69" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="50"/>
+    <cfRule type="aboveAverage" dxfId="30" priority="52" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C4">
+    <cfRule type="duplicateValues" dxfId="24" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1 I1:Z1">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C4">
-    <cfRule type="duplicateValues" dxfId="6" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="117"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_pengguna.xlsx
+++ b/data_pengguna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F5C94D-3273-469B-B870-11A5D610E3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291333BD-3EAB-43C1-9708-3A60C0351BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FBB3284E-7124-44F4-ACFD-447A6886AA12}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>NO REGISTRASI</t>
   </si>
@@ -175,6 +175,27 @@
   </si>
   <si>
     <t>Gd. Jendral Sudiman</t>
+  </si>
+  <si>
+    <t>PU 3</t>
+  </si>
+  <si>
+    <t>PK 3</t>
+  </si>
+  <si>
+    <t>PPU 3</t>
+  </si>
+  <si>
+    <t>PBM 3</t>
+  </si>
+  <si>
+    <t>Lit Bhs Indo 3</t>
+  </si>
+  <si>
+    <t>Lit Bhs Ing 3</t>
+  </si>
+  <si>
+    <t>PM 3</t>
   </si>
 </sst>
 </file>
@@ -1706,7 +1727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E436D765-1505-4BA4-BDA9-9A238174077E}">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="8" bestFit="1" customWidth="1"/>
@@ -1720,7 +1741,7 @@
     <col min="10" max="10" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -1799,8 +1820,29 @@
       <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG1" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
@@ -1886,8 +1928,29 @@
         <f>S2-4</f>
         <v>629</v>
       </c>
+      <c r="AA2">
+        <v>876</v>
+      </c>
+      <c r="AB2">
+        <v>876</v>
+      </c>
+      <c r="AC2">
+        <v>876</v>
+      </c>
+      <c r="AD2">
+        <v>876</v>
+      </c>
+      <c r="AE2">
+        <v>876</v>
+      </c>
+      <c r="AF2">
+        <v>876</v>
+      </c>
+      <c r="AG2">
+        <v>876</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>27</v>
       </c>
@@ -1973,8 +2036,29 @@
         <f t="shared" ref="Z3:Z4" si="6">S3-4</f>
         <v>629</v>
       </c>
+      <c r="AA3">
+        <v>876</v>
+      </c>
+      <c r="AB3">
+        <v>876</v>
+      </c>
+      <c r="AC3">
+        <v>876</v>
+      </c>
+      <c r="AD3">
+        <v>876</v>
+      </c>
+      <c r="AE3">
+        <v>876</v>
+      </c>
+      <c r="AF3">
+        <v>876</v>
+      </c>
+      <c r="AG3">
+        <v>876</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>28</v>
       </c>
@@ -2059,6 +2143,27 @@
       <c r="Z4">
         <f t="shared" si="6"/>
         <v>629</v>
+      </c>
+      <c r="AA4">
+        <v>876</v>
+      </c>
+      <c r="AB4">
+        <v>876</v>
+      </c>
+      <c r="AC4">
+        <v>876</v>
+      </c>
+      <c r="AD4">
+        <v>876</v>
+      </c>
+      <c r="AE4">
+        <v>876</v>
+      </c>
+      <c r="AF4">
+        <v>876</v>
+      </c>
+      <c r="AG4">
+        <v>876</v>
       </c>
     </row>
   </sheetData>
@@ -2072,122 +2177,122 @@
     <cfRule type="duplicateValues" dxfId="104" priority="7"/>
     <cfRule type="duplicateValues" dxfId="103" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:Z1">
-    <cfRule type="duplicateValues" dxfId="102" priority="111"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="101" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="105"/>
     <cfRule type="duplicateValues" dxfId="66" priority="106"/>
     <cfRule type="duplicateValues" dxfId="65" priority="107"/>
     <cfRule type="duplicateValues" dxfId="64" priority="108"/>
     <cfRule type="duplicateValues" dxfId="63" priority="109"/>
     <cfRule type="duplicateValues" dxfId="62" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="60" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="62"/>
-    <cfRule type="aboveAverage" dxfId="55" priority="34" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="68"/>
-    <cfRule type="aboveAverage" dxfId="49" priority="69" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="50"/>
-    <cfRule type="aboveAverage" dxfId="30" priority="52" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="57"/>
+    <cfRule type="aboveAverage" dxfId="61" priority="34" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="51"/>
+    <cfRule type="aboveAverage" dxfId="43" priority="52" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="68"/>
+    <cfRule type="aboveAverage" dxfId="26" priority="69" aboveAverage="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C4">
-    <cfRule type="duplicateValues" dxfId="24" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
     <cfRule type="duplicateValues" dxfId="18" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1 I1:Z1">
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="A1:AG1">
+    <cfRule type="duplicateValues" dxfId="3" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1 I1:AG1">
+    <cfRule type="duplicateValues" dxfId="2" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_pengguna.xlsx
+++ b/data_pengguna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291333BD-3EAB-43C1-9708-3A60C0351BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6497EE8-DF85-4EDC-950D-43365B31DA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FBB3284E-7124-44F4-ACFD-447A6886AA12}"/>
   </bookViews>
@@ -2295,5 +2295,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="123"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data_pengguna.xlsx
+++ b/data_pengguna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6497EE8-DF85-4EDC-950D-43365B31DA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A831AF11-202C-4D4E-9B6A-3EBF22C03CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FBB3284E-7124-44F4-ACFD-447A6886AA12}"/>
   </bookViews>

--- a/data_pengguna.xlsx
+++ b/data_pengguna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A831AF11-202C-4D4E-9B6A-3EBF22C03CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363BC419-30E0-466F-B86F-5A2050F62A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FBB3284E-7124-44F4-ACFD-447A6886AA12}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
   <si>
     <t>NO REGISTRASI</t>
   </si>
@@ -196,6 +196,18 @@
   </si>
   <si>
     <t>PM 3</t>
+  </si>
+  <si>
+    <t>PASSWORD</t>
+  </si>
+  <si>
+    <t>26111988</t>
+  </si>
+  <si>
+    <t>01012000</t>
+  </si>
+  <si>
+    <t>04041994</t>
   </si>
 </sst>
 </file>
@@ -278,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -302,6 +314,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1727,209 +1742,213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E436D765-1505-4BA4-BDA9-9A238174077E}">
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12" style="8" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>0</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>44</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>45</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>46</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>49</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>654</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>653</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>650</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>664</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>663</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>661</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>633</v>
       </c>
-      <c r="T2">
-        <f>M2+5</f>
+      <c r="U2">
+        <f>N2+5</f>
         <v>659</v>
       </c>
-      <c r="U2">
-        <f>N2+6</f>
+      <c r="V2">
+        <f>O2+6</f>
         <v>659</v>
       </c>
-      <c r="V2">
-        <f>O2+7</f>
+      <c r="W2">
+        <f>P2+7</f>
         <v>657</v>
       </c>
-      <c r="W2">
-        <f>P2+9</f>
+      <c r="X2">
+        <f>Q2+9</f>
         <v>673</v>
       </c>
-      <c r="X2">
-        <f>Q2-4</f>
+      <c r="Y2">
+        <f>R2-4</f>
         <v>659</v>
       </c>
-      <c r="Y2">
-        <f>R2+7</f>
+      <c r="Z2">
+        <f>S2+7</f>
         <v>668</v>
       </c>
-      <c r="Z2">
-        <f>S2-4</f>
+      <c r="AA2">
+        <f>T2-4</f>
         <v>629</v>
-      </c>
-      <c r="AA2">
-        <v>876</v>
       </c>
       <c r="AB2">
         <v>876</v>
@@ -1949,95 +1968,98 @@
       <c r="AG2">
         <v>876</v>
       </c>
+      <c r="AH2">
+        <v>876</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>11122222223</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>44</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>45</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>47</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>49</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>654</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>645</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>651</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>664</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>663</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>661</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>633</v>
       </c>
-      <c r="T3">
-        <f t="shared" ref="T3:T4" si="0">M3+5</f>
+      <c r="U3">
+        <f t="shared" ref="U3:U4" si="0">N3+5</f>
         <v>659</v>
       </c>
-      <c r="U3">
-        <f t="shared" ref="U3:U4" si="1">N3+6</f>
+      <c r="V3">
+        <f t="shared" ref="V3:V4" si="1">O3+6</f>
         <v>651</v>
       </c>
-      <c r="V3">
-        <f t="shared" ref="V3:V4" si="2">O3+7</f>
+      <c r="W3">
+        <f t="shared" ref="W3:W4" si="2">P3+7</f>
         <v>658</v>
       </c>
-      <c r="W3">
-        <f t="shared" ref="W3:W4" si="3">P3+9</f>
+      <c r="X3">
+        <f t="shared" ref="X3:X4" si="3">Q3+9</f>
         <v>673</v>
       </c>
-      <c r="X3">
-        <f t="shared" ref="X3:X4" si="4">Q3-4</f>
+      <c r="Y3">
+        <f t="shared" ref="Y3:Y4" si="4">R3-4</f>
         <v>659</v>
       </c>
-      <c r="Y3">
-        <f t="shared" ref="Y3:Y4" si="5">R3+7</f>
+      <c r="Z3">
+        <f t="shared" ref="Z3:Z4" si="5">S3+7</f>
         <v>668</v>
       </c>
-      <c r="Z3">
-        <f t="shared" ref="Z3:Z4" si="6">S3-4</f>
+      <c r="AA3">
+        <f t="shared" ref="AA3:AA4" si="6">T3-4</f>
         <v>629</v>
-      </c>
-      <c r="AA3">
-        <v>876</v>
       </c>
       <c r="AB3">
         <v>876</v>
@@ -2057,96 +2079,99 @@
       <c r="AG3">
         <v>876</v>
       </c>
+      <c r="AH3">
+        <v>876</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>12312312344</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>44</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>45</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>48</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>49</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>654</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>637</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>652</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>664</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>663</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>661</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>633</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <f t="shared" si="0"/>
         <v>659</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <f t="shared" si="1"/>
         <v>643</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <f t="shared" si="2"/>
         <v>659</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <f t="shared" si="3"/>
         <v>673</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <f t="shared" si="4"/>
         <v>659</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <f t="shared" si="5"/>
         <v>668</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <f t="shared" si="6"/>
         <v>629</v>
       </c>
-      <c r="AA4">
-        <v>876</v>
-      </c>
       <c r="AB4">
         <v>876</v>
       </c>
@@ -2163,6 +2188,9 @@
         <v>876</v>
       </c>
       <c r="AG4">
+        <v>876</v>
+      </c>
+      <c r="AH4">
         <v>876</v>
       </c>
     </row>
@@ -2177,119 +2205,119 @@
     <cfRule type="duplicateValues" dxfId="104" priority="7"/>
     <cfRule type="duplicateValues" dxfId="103" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="102" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="110"/>
+  <conditionalFormatting sqref="A1 C1:AH1">
+    <cfRule type="duplicateValues" dxfId="102" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="aboveAverage" dxfId="61" priority="34" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="51"/>
-    <cfRule type="aboveAverage" dxfId="43" priority="52" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="68"/>
-    <cfRule type="aboveAverage" dxfId="26" priority="69" aboveAverage="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C4">
-    <cfRule type="duplicateValues" dxfId="25" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="118"/>
+    <cfRule type="aboveAverage" dxfId="60" priority="34" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="51"/>
+    <cfRule type="aboveAverage" dxfId="42" priority="52" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="68"/>
+    <cfRule type="aboveAverage" dxfId="25" priority="69" aboveAverage="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
+  <conditionalFormatting sqref="D1:D4">
+    <cfRule type="duplicateValues" dxfId="24" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AG1">
-    <cfRule type="duplicateValues" dxfId="3" priority="119"/>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1 I1:AG1">
+  <conditionalFormatting sqref="G1">
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 J1:AH1">
     <cfRule type="duplicateValues" dxfId="2" priority="121"/>
     <cfRule type="duplicateValues" dxfId="1" priority="122"/>
     <cfRule type="duplicateValues" dxfId="0" priority="123"/>

--- a/data_pengguna.xlsx
+++ b/data_pengguna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363BC419-30E0-466F-B86F-5A2050F62A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5BBBCC-0877-4F52-971D-A85D039F80EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FBB3284E-7124-44F4-ACFD-447A6886AA12}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
   <si>
     <t>NO REGISTRASI</t>
   </si>
@@ -111,9 +111,6 @@
     <t>89999999999</t>
   </si>
   <si>
-    <t>87771740512</t>
-  </si>
-  <si>
     <t>A-123</t>
   </si>
   <si>
@@ -129,36 +126,24 @@
     <t>BB BBB BBB</t>
   </si>
   <si>
-    <t>AAA AAA AAA</t>
-  </si>
-  <si>
     <t>81234567891</t>
   </si>
   <si>
     <t>89999999998</t>
   </si>
   <si>
-    <t>87771740511</t>
-  </si>
-  <si>
     <t>Ibu XXX</t>
   </si>
   <si>
     <t>Bapak BBB</t>
   </si>
   <si>
-    <t>Ibu ABC</t>
-  </si>
-  <si>
     <t>10 REG A 1</t>
   </si>
   <si>
     <t>11 UTBK A 5</t>
   </si>
   <si>
-    <t>12 UTBK B-5</t>
-  </si>
-  <si>
     <t>SEN-SEL-RAB</t>
   </si>
   <si>
@@ -208,6 +193,24 @@
   </si>
   <si>
     <t>04041994</t>
+  </si>
+  <si>
+    <t>87787256428</t>
+  </si>
+  <si>
+    <t>Sisca Aprina</t>
+  </si>
+  <si>
+    <t>XXX XXXXXX</t>
+  </si>
+  <si>
+    <t>0212345678</t>
+  </si>
+  <si>
+    <t>CS - Admin</t>
+  </si>
+  <si>
+    <t>Senin - Sabtu</t>
   </si>
 </sst>
 </file>
@@ -1762,7 +1765,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1840,25 +1843,25 @@
         <v>24</v>
       </c>
       <c r="AB1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH1" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
@@ -1866,19 +1869,19 @@
         <v>26</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>26</v>
@@ -1887,89 +1890,89 @@
         <v>0</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" t="s">
         <v>41</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>44</v>
-      </c>
-      <c r="K2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M2" t="s">
-        <v>49</v>
       </c>
       <c r="N2">
         <v>654</v>
       </c>
       <c r="O2">
-        <v>653</v>
+        <v>600</v>
       </c>
       <c r="P2">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="Q2">
-        <v>664</v>
+        <v>533</v>
       </c>
       <c r="R2">
-        <v>663</v>
+        <v>865</v>
       </c>
       <c r="S2">
-        <v>661</v>
+        <v>452</v>
       </c>
       <c r="T2">
-        <v>633</v>
+        <v>422</v>
       </c>
       <c r="U2">
-        <f>N2+5</f>
+        <f t="shared" ref="U2" si="0">N2+5</f>
         <v>659</v>
       </c>
       <c r="V2">
-        <f>O2+6</f>
-        <v>659</v>
+        <f t="shared" ref="V2" si="1">O2+6</f>
+        <v>606</v>
       </c>
       <c r="W2">
-        <f>P2+7</f>
-        <v>657</v>
+        <f t="shared" ref="W2" si="2">P2+7</f>
+        <v>640</v>
       </c>
       <c r="X2">
-        <f>Q2+9</f>
-        <v>673</v>
+        <f t="shared" ref="X2" si="3">Q2+9</f>
+        <v>542</v>
       </c>
       <c r="Y2">
-        <f>R2-4</f>
-        <v>659</v>
+        <f t="shared" ref="Y2" si="4">R2-4</f>
+        <v>861</v>
       </c>
       <c r="Z2">
-        <f>S2+7</f>
-        <v>668</v>
+        <f t="shared" ref="Z2" si="5">S2+7</f>
+        <v>459</v>
       </c>
       <c r="AA2">
-        <f>T2-4</f>
-        <v>629</v>
+        <f t="shared" ref="AA2" si="6">T2-4</f>
+        <v>418</v>
       </c>
       <c r="AB2">
-        <v>876</v>
+        <v>677</v>
       </c>
       <c r="AC2">
-        <v>876</v>
+        <v>845</v>
       </c>
       <c r="AD2">
-        <v>876</v>
+        <v>324</v>
       </c>
       <c r="AE2">
-        <v>876</v>
+        <v>684</v>
       </c>
       <c r="AF2">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>876</v>
+        <v>764</v>
       </c>
       <c r="AH2">
-        <v>876</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
@@ -1977,19 +1980,19 @@
         <v>27</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>27</v>
@@ -1998,19 +2001,19 @@
         <v>11122222223</v>
       </c>
       <c r="I3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" t="s">
         <v>42</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>44</v>
-      </c>
-      <c r="K3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" t="s">
-        <v>49</v>
       </c>
       <c r="N3">
         <v>654</v>
@@ -2034,31 +2037,31 @@
         <v>633</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U4" si="0">N3+5</f>
+        <f t="shared" ref="U3:U4" si="7">N3+5</f>
         <v>659</v>
       </c>
       <c r="V3">
-        <f t="shared" ref="V3:V4" si="1">O3+6</f>
+        <f t="shared" ref="V3:V4" si="8">O3+6</f>
         <v>651</v>
       </c>
       <c r="W3">
-        <f t="shared" ref="W3:W4" si="2">P3+7</f>
+        <f t="shared" ref="W3:W4" si="9">P3+7</f>
         <v>658</v>
       </c>
       <c r="X3">
-        <f t="shared" ref="X3:X4" si="3">Q3+9</f>
+        <f t="shared" ref="X3:X4" si="10">Q3+9</f>
         <v>673</v>
       </c>
       <c r="Y3">
-        <f t="shared" ref="Y3:Y4" si="4">R3-4</f>
+        <f t="shared" ref="Y3:Y4" si="11">R3-4</f>
         <v>659</v>
       </c>
       <c r="Z3">
-        <f t="shared" ref="Z3:Z4" si="5">S3+7</f>
+        <f t="shared" ref="Z3:Z4" si="12">S3+7</f>
         <v>668</v>
       </c>
       <c r="AA3">
-        <f t="shared" ref="AA3:AA4" si="6">T3-4</f>
+        <f t="shared" ref="AA3:AA4" si="13">T3-4</f>
         <v>629</v>
       </c>
       <c r="AB3">
@@ -2085,146 +2088,146 @@
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3">
         <v>12312312344</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" t="s">
         <v>43</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>44</v>
-      </c>
-      <c r="K4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" t="s">
-        <v>49</v>
       </c>
       <c r="N4">
         <v>654</v>
       </c>
       <c r="O4">
-        <v>637</v>
+        <v>600</v>
       </c>
       <c r="P4">
-        <v>652</v>
+        <v>633</v>
       </c>
       <c r="Q4">
-        <v>664</v>
+        <v>533</v>
       </c>
       <c r="R4">
-        <v>663</v>
+        <v>865</v>
       </c>
       <c r="S4">
-        <v>661</v>
+        <v>452</v>
       </c>
       <c r="T4">
-        <v>633</v>
+        <v>422</v>
       </c>
       <c r="U4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>659</v>
       </c>
       <c r="V4">
-        <f t="shared" si="1"/>
-        <v>643</v>
+        <f t="shared" si="8"/>
+        <v>606</v>
       </c>
       <c r="W4">
-        <f t="shared" si="2"/>
-        <v>659</v>
+        <f t="shared" si="9"/>
+        <v>640</v>
       </c>
       <c r="X4">
-        <f t="shared" si="3"/>
-        <v>673</v>
+        <f t="shared" si="10"/>
+        <v>542</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="4"/>
-        <v>659</v>
+        <f t="shared" si="11"/>
+        <v>861</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="5"/>
-        <v>668</v>
+        <f t="shared" si="12"/>
+        <v>459</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="6"/>
-        <v>629</v>
+        <f t="shared" si="13"/>
+        <v>418</v>
       </c>
       <c r="AB4">
-        <v>876</v>
+        <v>677</v>
       </c>
       <c r="AC4">
-        <v>876</v>
+        <v>845</v>
       </c>
       <c r="AD4">
-        <v>876</v>
+        <v>324</v>
       </c>
       <c r="AE4">
-        <v>876</v>
+        <v>684</v>
       </c>
       <c r="AF4">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>876</v>
+        <v>764</v>
       </c>
       <c r="AH4">
-        <v>876</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1 C1:AH1">
+    <cfRule type="duplicateValues" dxfId="110" priority="119"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="110" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1 C1:AH1">
-    <cfRule type="duplicateValues" dxfId="102" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="101" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="78"/>
     <cfRule type="duplicateValues" dxfId="94" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="70"/>
     <cfRule type="duplicateValues" dxfId="85" priority="86"/>
     <cfRule type="duplicateValues" dxfId="84" priority="87"/>
     <cfRule type="duplicateValues" dxfId="83" priority="88"/>
@@ -2237,57 +2240,57 @@
     <cfRule type="duplicateValues" dxfId="76" priority="95"/>
     <cfRule type="duplicateValues" dxfId="75" priority="96"/>
     <cfRule type="duplicateValues" dxfId="74" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="85"/>
     <cfRule type="duplicateValues" dxfId="72" priority="99"/>
     <cfRule type="duplicateValues" dxfId="71" priority="100"/>
     <cfRule type="duplicateValues" dxfId="70" priority="101"/>
     <cfRule type="duplicateValues" dxfId="69" priority="102"/>
     <cfRule type="duplicateValues" dxfId="68" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="98"/>
     <cfRule type="duplicateValues" dxfId="66" priority="105"/>
     <cfRule type="duplicateValues" dxfId="65" priority="106"/>
     <cfRule type="duplicateValues" dxfId="64" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="aboveAverage" dxfId="60" priority="34" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="51"/>
-    <cfRule type="aboveAverage" dxfId="42" priority="52" aboveAverage="0"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="68"/>
-    <cfRule type="aboveAverage" dxfId="25" priority="69" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="68"/>
+    <cfRule type="aboveAverage" dxfId="52" priority="69" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="66"/>
+    <cfRule type="aboveAverage" dxfId="50" priority="34" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="51"/>
+    <cfRule type="aboveAverage" dxfId="33" priority="52" aboveAverage="0"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D4">
     <cfRule type="duplicateValues" dxfId="24" priority="112"/>
@@ -2298,24 +2301,24 @@
     <cfRule type="duplicateValues" dxfId="19" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="25"/>
     <cfRule type="duplicateValues" dxfId="15" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
     <cfRule type="duplicateValues" dxfId="11" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
     <cfRule type="duplicateValues" dxfId="5" priority="17"/>
     <cfRule type="duplicateValues" dxfId="4" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1 J1:AH1">
     <cfRule type="duplicateValues" dxfId="2" priority="121"/>

--- a/data_pengguna.xlsx
+++ b/data_pengguna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5BBBCC-0877-4F52-971D-A85D039F80EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E12960-B0FB-452E-9019-EA8A80A7D07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FBB3284E-7124-44F4-ACFD-447A6886AA12}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="69">
   <si>
     <t>NO REGISTRASI</t>
   </si>
@@ -198,9 +198,6 @@
     <t>87787256428</t>
   </si>
   <si>
-    <t>Sisca Aprina</t>
-  </si>
-  <si>
     <t>XXX XXXXXX</t>
   </si>
   <si>
@@ -211,6 +208,30 @@
   </si>
   <si>
     <t>Senin - Sabtu</t>
+  </si>
+  <si>
+    <t>Siska Aprina</t>
+  </si>
+  <si>
+    <t>82315310145</t>
+  </si>
+  <si>
+    <t>06061990</t>
+  </si>
+  <si>
+    <t>C-123</t>
+  </si>
+  <si>
+    <t>Sisca Anggraeni</t>
+  </si>
+  <si>
+    <t>Abc Abcde</t>
+  </si>
+  <si>
+    <t>8151515151</t>
+  </si>
+  <si>
+    <t>Admin - T</t>
   </si>
 </sst>
 </file>
@@ -1745,7 +1766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E436D765-1505-4BA4-BDA9-9A238174077E}">
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="8" bestFit="1" customWidth="1"/>
@@ -2097,25 +2118,25 @@
         <v>30</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>56</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>59</v>
       </c>
       <c r="H4" s="3">
         <v>12312312344</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" t="s">
         <v>60</v>
-      </c>
-      <c r="J4" t="s">
-        <v>61</v>
       </c>
       <c r="K4" t="s">
         <v>40</v>
@@ -2195,6 +2216,117 @@
       </c>
       <c r="AH4">
         <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="3">
+        <v>98765432100</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5">
+        <v>145</v>
+      </c>
+      <c r="O5">
+        <v>432</v>
+      </c>
+      <c r="P5">
+        <v>245</v>
+      </c>
+      <c r="Q5">
+        <v>234</v>
+      </c>
+      <c r="R5">
+        <v>234</v>
+      </c>
+      <c r="S5">
+        <v>562</v>
+      </c>
+      <c r="T5">
+        <v>233</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5" si="14">N5+5</f>
+        <v>150</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5" si="15">O5+6</f>
+        <v>438</v>
+      </c>
+      <c r="W5">
+        <f t="shared" ref="W5" si="16">P5+7</f>
+        <v>252</v>
+      </c>
+      <c r="X5">
+        <f t="shared" ref="X5" si="17">Q5+9</f>
+        <v>243</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" ref="Y5" si="18">R5-4</f>
+        <v>230</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" ref="Z5" si="19">S5+7</f>
+        <v>569</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" ref="AA5" si="20">T5-4</f>
+        <v>229</v>
+      </c>
+      <c r="AB5">
+        <v>543</v>
+      </c>
+      <c r="AC5">
+        <v>456</v>
+      </c>
+      <c r="AD5">
+        <v>566</v>
+      </c>
+      <c r="AE5">
+        <v>532</v>
+      </c>
+      <c r="AF5">
+        <v>109</v>
+      </c>
+      <c r="AG5">
+        <v>643</v>
+      </c>
+      <c r="AH5">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2424,7 @@
     <cfRule type="duplicateValues" dxfId="26" priority="59"/>
     <cfRule type="duplicateValues" dxfId="25" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D4">
+  <conditionalFormatting sqref="D1:D5">
     <cfRule type="duplicateValues" dxfId="24" priority="112"/>
     <cfRule type="duplicateValues" dxfId="23" priority="113"/>
     <cfRule type="duplicateValues" dxfId="22" priority="114"/>
